--- a/src/main/resources/DDT/Data.xlsx
+++ b/src/main/resources/DDT/Data.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\shashank\Capgemini_Training\Selenium\Adv_Selenium\selenium-advance\src\main\resources\DDT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B63B0BF4-C0ED-4230-8BCD-882FBEEFCFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1A00EE-1873-4B22-9A2B-ECC60BB68576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{77F40206-6188-46F7-88A0-A32B0F7E3BF9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{77F40206-6188-46F7-88A0-A32B0F7E3BF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
   <si>
     <t>browser</t>
   </si>
@@ -49,6 +50,27 @@
   </si>
   <si>
     <t>secret_sauce</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>shank</t>
+  </si>
+  <si>
+    <t>shashank</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t>abc</t>
+  </si>
+  <si>
+    <t>def</t>
+  </si>
+  <si>
+    <t>ijk</t>
   </si>
 </sst>
 </file>
@@ -449,4 +471,50 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08850874-F6E3-453C-81F6-18147E19AC04}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/DDT/Data.xlsx
+++ b/src/main/resources/DDT/Data.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\shashank\Capgemini_Training\Selenium\Adv_Selenium\selenium-advance\src\main\resources\DDT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A1A00EE-1873-4B22-9A2B-ECC60BB68576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F31C91B-9329-4128-98FF-518C3884A62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{77F40206-6188-46F7-88A0-A32B0F7E3BF9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{77F40206-6188-46F7-88A0-A32B0F7E3BF9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="54">
   <si>
     <t>browser</t>
   </si>
@@ -71,13 +72,130 @@
   </si>
   <si>
     <t>ijk</t>
+  </si>
+  <si>
+    <t>rahul</t>
+  </si>
+  <si>
+    <t>lmn</t>
+  </si>
+  <si>
+    <t>rohit</t>
+  </si>
+  <si>
+    <t>opq</t>
+  </si>
+  <si>
+    <t>amit</t>
+  </si>
+  <si>
+    <t>rst</t>
+  </si>
+  <si>
+    <t>arjun</t>
+  </si>
+  <si>
+    <t>uvw</t>
+  </si>
+  <si>
+    <t>vijay</t>
+  </si>
+  <si>
+    <t>xyz</t>
+  </si>
+  <si>
+    <t>Kiran</t>
+  </si>
+  <si>
+    <t>pqr</t>
+  </si>
+  <si>
+    <t>priya</t>
+  </si>
+  <si>
+    <t>stu</t>
+  </si>
+  <si>
+    <t>sneha</t>
+  </si>
+  <si>
+    <t>vwx</t>
+  </si>
+  <si>
+    <t>ananya</t>
+  </si>
+  <si>
+    <t>yza</t>
+  </si>
+  <si>
+    <t>neha</t>
+  </si>
+  <si>
+    <t>bcd</t>
+  </si>
+  <si>
+    <t>pooja</t>
+  </si>
+  <si>
+    <t>efg</t>
+  </si>
+  <si>
+    <t>varun</t>
+  </si>
+  <si>
+    <t>hij</t>
+  </si>
+  <si>
+    <t>shank@gmail.com</t>
+  </si>
+  <si>
+    <t>shashank@gmail.com</t>
+  </si>
+  <si>
+    <t>xxx@gmail.com</t>
+  </si>
+  <si>
+    <t>rahul@gmail.com</t>
+  </si>
+  <si>
+    <t>rohit@gmail.com</t>
+  </si>
+  <si>
+    <t>amit@gmail.com</t>
+  </si>
+  <si>
+    <t>arjun@gmail.com</t>
+  </si>
+  <si>
+    <t>vijay@gmail.com</t>
+  </si>
+  <si>
+    <t>Kiran@gmail.com</t>
+  </si>
+  <si>
+    <t>priya@gmail.com</t>
+  </si>
+  <si>
+    <t>sneha@gmail.com</t>
+  </si>
+  <si>
+    <t>ananya@gmail.com</t>
+  </si>
+  <si>
+    <t>neha@gmail.com</t>
+  </si>
+  <si>
+    <t>pooja@gmail.com</t>
+  </si>
+  <si>
+    <t>qwerty@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,6 +208,22 @@
       <color rgb="FFCE9178"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,16 +243,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -475,7 +620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08850874-F6E3-453C-81F6-18147E19AC04}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.44140625" customWidth="1"/>
@@ -483,38 +628,294 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
     </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3046F854-C13D-4D63-9073-9207C9830F29}">
+  <dimension ref="A1:B16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.44140625" customWidth="1"/>
+    <col min="2" max="2" width="24.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{917A3529-F8FA-4E9A-9A88-434F0CDE8A76}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{789F2627-F580-4171-9BB6-BF96E51C46E9}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{D2E51CCE-50FA-40B2-83F7-F21427BA2B93}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{AA08B7AD-2DA2-4134-827E-A757CBB8D904}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{E50EB0ED-B169-4BC5-AB30-0763E2C58AF1}"/>
+    <hyperlink ref="A7" r:id="rId6" xr:uid="{8D2E71B4-A598-47AF-A617-F6F48807C74D}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{9B1EEB56-8E66-4AFA-A522-787342115E9D}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{BD951353-8FC8-4967-9455-8437B5FA2612}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{580F394F-8066-4F27-A306-66DCF9641D9E}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{8A1478EE-3242-4792-9087-A8B4D86449AF}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{F87DDDDD-4F76-41E1-A0BF-D8253FEFA8DB}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{C0D41DF9-0C58-49C7-8E43-852B235E9F78}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{92875B2D-4CCE-453F-A189-7B3DB31DD417}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{3F955CC6-56B4-446C-BE4A-57047BD87209}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{0A5F48E8-C0C6-4BA3-A9DA-38EA32BED586}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>